--- a/ch_07/ch_07_solutions.xlsx
+++ b/ch_07/ch_07_solutions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30501"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_07_forecasting_time_series\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C632B75-B256-4746-9F32-2E261DDAA222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1118BB5-F6B0-45B5-8C4E-F4F80CC7692B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" firstSheet="1" activeTab="1" xr2:uid="{127BCBE3-2501-4C38-9896-5064F2DA9264}"/>
   </bookViews>
@@ -638,15 +638,6 @@
 plt.tight_layout()</code>
     </pythonScript>
     <pythonScript>
-      <code>from statsmodels.tsa.stattools import adfuller
-result = adfuller(passengers_df['passengers'].dropna())
-results_df = pd.DataFrame({
-    'Metric': ['Test Statistic', 'p-value'],
-    'Value': [result[0], result[1]]
-})
-results_df</code>
-    </pythonScript>
-    <pythonScript>
       <code xml:space="preserve"># Split data into training and test sets 
 train_data = passengers_df[ 
 passengers_df.index &lt; '1959-01-01' 
@@ -668,8 +659,10 @@
 hw_fit_train = hw_model_train.fit() </code>
     </pythonScript>
     <pythonScript>
-      <code>forecast_test = hw_fit_train.forecast(steps=len(test_data))
-forecast_test.head()</code>
+      <code xml:space="preserve">forecast_test = hw_fit_train.forecast(steps=len(test_data)) 
+comparison = test_data[['passengers']].copy() 
+comparison['forecast'] = forecast_test 
+comparison.head() </code>
     </pythonScript>
     <pythonScript>
       <code>errors = np.abs(forecast_test.values - test_data['passengers'].values)
@@ -685,18 +678,11 @@
 comparison_df</code>
     </pythonScript>
     <pythonScript>
-      <code xml:space="preserve"># Create a naive baseline forecast using the last observed value 
-baseline_forecast = np.repeat( 
-train_data['passengers'].iloc[-1], 
-len(test_data) 
-) 
-# Compute absolute errors 
-baseline_errors = np.abs( 
-baseline_forecast - test_data['passengers'].values 
-) 
-# Calculate Mean Absolute Error (MAE) 
-baseline_mae = np.mean(baseline_errors) 
-</code>
+      <code>last_value = train_data['passengers'].iloc[-1]
+baseline_forecast = pd.Series(last_value, index=test_data.index)
+baseline_errors = (baseline_forecast - test_data['passengers']).abs()
+baseline_mae = baseline_errors.mean()
+f"Baseline MAE: {baseline_mae:.2f}"</code>
     </pythonScript>
     <pythonScript>
       <code>hw_improvement = (baseline_mae - mae) / baseline_mae * 100
@@ -1757,14 +1743,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1001889</xdr:colOff>
-      <xdr:row>102</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>254001</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>144508</xdr:colOff>
-      <xdr:row>117</xdr:row>
-      <xdr:rowOff>857</xdr:rowOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>858</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1779,7 +1765,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="passengers_ts!A104"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="passengers_ts!A93"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1806,13 +1792,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>135</xdr:row>
+      <xdr:row>124</xdr:row>
       <xdr:rowOff>14111</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>144509</xdr:colOff>
-      <xdr:row>149</xdr:row>
+      <xdr:row>138</xdr:row>
       <xdr:rowOff>64355</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1828,7 +1814,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="passengers_ts!A136"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="passengers_ts!A125"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1855,13 +1841,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1524000</xdr:colOff>
-      <xdr:row>196</xdr:row>
+      <xdr:row>182</xdr:row>
       <xdr:rowOff>261054</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>666619</xdr:colOff>
-      <xdr:row>211</xdr:row>
+      <xdr:row>197</xdr:row>
       <xdr:rowOff>7910</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1877,7 +1863,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="passengers_ts!A196"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="passengers_ts!A182"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1904,13 +1890,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>2088445</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>91722</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>141112</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>62</xdr:row>
       <xdr:rowOff>60478</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1926,7 +1912,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="passengers_ts!A60"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="passengers_ts!A49"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -2011,8 +1997,8 @@
       <xdr:rowOff>8467</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>637721</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>939346</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>84676</xdr:rowOff>
     </xdr:to>
@@ -2060,8 +2046,8 @@
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>914993</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>224431</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>89542</xdr:rowOff>
     </xdr:to>
@@ -2374,7 +2360,7 @@
   <rv s="3">
     <v>&lt;class 'statsmodels.tsa.holtwinters.results.HoltWintersResultsWrapper'&gt;</v>
     <v>HoltWintersResultsWrapper</v>
-    <v>&lt;statsmodels.tsa.holtwinters.results.HoltWintersResultsWrapper object at 0x7f63d8a76900&gt;</v>
+    <v>&lt;statsmodels.tsa.holtwinters.results.HoltWintersResultsWrapper object at 0x7f052781d9a0&gt;</v>
     <v>1</v>
   </rv>
   <rv s="8">
@@ -2385,12 +2371,12 @@
     <v>Mean Absolute Error: 31.07</v>
     <v>1</v>
   </rv>
-  <rv s="9">
-    <fb>115.25</fb>
-    <v>&lt;class 'numpy.float64'&gt;</v>
-    <v>float64</v>
-    <v>115.25</v>
-    <v>115.25</v>
+  <rv s="8">
+    <fb t="s">Baseline MAE: 115.25</fb>
+    <v>&lt;class 'str'&gt;</v>
+    <v>str</v>
+    <v>Baseline MAE: 115.25</v>
+    <v>Baseline MAE: 115.25</v>
     <v>1</v>
   </rv>
   <rv s="2">
@@ -2432,7 +2418,7 @@
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <s t="_error">
     <k n="errorType" t="i"/>
   </s>
@@ -2476,13 +2462,6 @@
     <k n="Python_typeName" t="s"/>
     <k n="Python_str" t="s"/>
     <k n="basicValue" t="s"/>
-    <k n="_Provider" t="spb"/>
-  </s>
-  <s t="_python">
-    <k n="Python_type" t="s"/>
-    <k n="Python_typeName" t="s"/>
-    <k n="Python_str" t="s"/>
-    <k n="basicValue"/>
     <k n="_Provider" t="spb"/>
   </s>
 </rvStructures>
@@ -4078,7 +4057,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4D059EF-DBD7-449D-AE98-3E439228E9FA}">
-  <dimension ref="A1:C196"/>
+  <dimension ref="A1:C182"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="18.9140625" style="3" customWidth="1"/>
@@ -4233,901 +4212,919 @@
         <v>#VALUE!</v>
       </c>
     </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A33" s="3" t="str" cm="1">
+        <f t="array" aca="1" ref="A33:C46" ca="1">_xlfn._xlws.PY(3,0)</f>
+        <v/>
+      </c>
+      <c r="B33" t="str">
+        <f ca="1"/>
+        <v>passengers</v>
+      </c>
+      <c r="C33" s="6" t="str">
+        <f ca="1"/>
+        <v>rolling_mean</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A34" s="3" t="str">
+        <f ca="1"/>
+        <v>date</v>
+      </c>
+      <c r="B34" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="C34" s="6" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A35" s="3" vm="2">
+        <f ca="1"/>
+        <v>17899</v>
+      </c>
+      <c r="B35">
+        <f ca="1"/>
+        <v>112</v>
+      </c>
+      <c r="C35" s="6" t="e">
+        <f ca="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A36" s="3" vm="3">
+        <f ca="1"/>
+        <v>17930</v>
+      </c>
+      <c r="B36">
+        <f ca="1"/>
+        <v>118</v>
+      </c>
+      <c r="C36" s="6" t="e">
+        <f ca="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A37" s="3" vm="4">
+        <f ca="1"/>
+        <v>17958</v>
+      </c>
+      <c r="B37">
+        <f ca="1"/>
+        <v>132</v>
+      </c>
+      <c r="C37" s="6" t="e">
+        <f ca="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A38" s="3" vm="5">
+        <f ca="1"/>
+        <v>17989</v>
+      </c>
+      <c r="B38">
+        <f ca="1"/>
+        <v>129</v>
+      </c>
+      <c r="C38" s="6" t="e">
+        <f ca="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A39" s="3" vm="6">
+        <f ca="1"/>
+        <v>18019</v>
+      </c>
+      <c r="B39">
+        <f ca="1"/>
+        <v>121</v>
+      </c>
+      <c r="C39" s="6" t="e">
+        <f ca="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A40" s="3" vm="13">
+        <f ca="1"/>
+        <v>18050</v>
+      </c>
+      <c r="B40">
+        <f ca="1"/>
+        <v>135</v>
+      </c>
+      <c r="C40" s="6" t="e">
+        <f ca="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A41" s="3" vm="14">
+        <f ca="1"/>
+        <v>18080</v>
+      </c>
+      <c r="B41">
+        <f ca="1"/>
+        <v>148</v>
+      </c>
+      <c r="C41" s="6" t="e">
+        <f ca="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A42" s="3" vm="15">
+        <f ca="1"/>
+        <v>18111</v>
+      </c>
+      <c r="B42">
+        <f ca="1"/>
+        <v>148</v>
+      </c>
+      <c r="C42" s="6" t="e">
+        <f ca="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A43" s="3" vm="16">
+        <f ca="1"/>
+        <v>18142</v>
+      </c>
+      <c r="B43">
+        <f ca="1"/>
+        <v>136</v>
+      </c>
+      <c r="C43" s="6" t="e">
+        <f ca="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A44" s="3" t="str" cm="1">
-        <f t="array" aca="1" ref="A44:C57" ca="1">_xlfn._xlws.PY(3,0)</f>
+      <c r="A44" s="3" vm="17">
+        <f ca="1"/>
+        <v>18172</v>
+      </c>
+      <c r="B44">
+        <f ca="1"/>
+        <v>119</v>
+      </c>
+      <c r="C44" s="6" t="e">
+        <f ca="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A45" s="3" vm="18">
+        <f ca="1"/>
+        <v>18203</v>
+      </c>
+      <c r="B45">
+        <f ca="1"/>
+        <v>104</v>
+      </c>
+      <c r="C45" s="6" t="e">
+        <f ca="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A46" s="3" vm="19">
+        <f ca="1"/>
+        <v>18233</v>
+      </c>
+      <c r="B46">
+        <f ca="1"/>
+        <v>118</v>
+      </c>
+      <c r="C46" s="6">
+        <f ca="1"/>
+        <v>126.66666666666667</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="C47" s="6"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.7">
+      <c r="A49" s="3" t="e" cm="1" vm="20">
+        <f t="array" aca="1" ref="A49" ca="1">_xlfn._xlws.PY(4,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A75" s="3" t="str" cm="1">
+        <f t="array" aca="1" ref="A75:B90" ca="1">_xlfn._xlws.PY(5,0)</f>
+        <v>date</v>
+      </c>
+      <c r="B75" s="5" t="str">
+        <f ca="1"/>
+        <v>trend</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A76" s="3" vm="2">
+        <f ca="1"/>
+        <v>17899</v>
+      </c>
+      <c r="B76" s="5" t="e">
+        <f ca="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A77" s="3" vm="3">
+        <f ca="1"/>
+        <v>17930</v>
+      </c>
+      <c r="B77" s="5" t="e">
+        <f ca="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A78" s="3" vm="4">
+        <f ca="1"/>
+        <v>17958</v>
+      </c>
+      <c r="B78" s="5" t="e">
+        <f ca="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A79" s="3" vm="5">
+        <f ca="1"/>
+        <v>17989</v>
+      </c>
+      <c r="B79" s="5" t="e">
+        <f ca="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A80" s="3" vm="6">
+        <f ca="1"/>
+        <v>18019</v>
+      </c>
+      <c r="B80" s="5" t="e">
+        <f ca="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A81" s="3" vm="13">
+        <f ca="1"/>
+        <v>18050</v>
+      </c>
+      <c r="B81" s="5" t="e">
+        <f ca="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A82" s="3" vm="14">
+        <f ca="1"/>
+        <v>18080</v>
+      </c>
+      <c r="B82" s="5">
+        <f ca="1"/>
+        <v>126.79166666666666</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A83" s="3" vm="15">
+        <f ca="1"/>
+        <v>18111</v>
+      </c>
+      <c r="B83" s="5">
+        <f ca="1"/>
+        <v>127.24999999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A84" s="3" vm="16">
+        <f ca="1"/>
+        <v>18142</v>
+      </c>
+      <c r="B84" s="5">
+        <f ca="1"/>
+        <v>127.95833333333331</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A85" s="3" vm="17">
+        <f ca="1"/>
+        <v>18172</v>
+      </c>
+      <c r="B85" s="5">
+        <f ca="1"/>
+        <v>128.58333333333331</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A86" s="3" vm="18">
+        <f ca="1"/>
+        <v>18203</v>
+      </c>
+      <c r="B86" s="5">
+        <f ca="1"/>
+        <v>128.99999999999997</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A87" s="3" vm="19">
+        <f ca="1"/>
+        <v>18233</v>
+      </c>
+      <c r="B87" s="5">
+        <f ca="1"/>
+        <v>129.75</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A88" s="3" vm="21">
+        <f ca="1"/>
+        <v>18264</v>
+      </c>
+      <c r="B88" s="5">
+        <f ca="1"/>
+        <v>131.25</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A89" s="3" vm="22">
+        <f ca="1"/>
+        <v>18295</v>
+      </c>
+      <c r="B89" s="5">
+        <f ca="1"/>
+        <v>133.08333333333334</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A90" s="3" vm="23">
+        <f ca="1"/>
+        <v>18323</v>
+      </c>
+      <c r="B90" s="5">
+        <f ca="1"/>
+        <v>134.91666666666669</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A93" s="3" t="e" cm="1" vm="24">
+        <f t="array" aca="1" ref="A93" ca="1">_xlfn._xlws.PY(6,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="B108" s="6"/>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A109" s="3" t="str" cm="1">
+        <f t="array" aca="1" ref="A109:C120" ca="1">_xlfn._xlws.PY(7,0)</f>
         <v/>
       </c>
-      <c r="B44" t="str">
+      <c r="B109" s="6" t="str">
         <f ca="1"/>
         <v>passengers</v>
       </c>
-      <c r="C44" s="6" t="str">
-        <f ca="1"/>
-        <v>rolling_mean</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A45" s="3" t="str">
+      <c r="C109" t="str">
+        <f ca="1"/>
+        <v>fitted</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A110" s="3" t="str">
         <f ca="1"/>
         <v>date</v>
       </c>
-      <c r="B45" t="str">
+      <c r="B110" s="6" t="str">
         <f ca="1"/>
         <v/>
       </c>
-      <c r="C45" s="6" t="str">
+      <c r="C110" t="str">
         <f ca="1"/>
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A46" s="3" vm="2">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A111" s="3" vm="2">
         <f ca="1"/>
         <v>17899</v>
       </c>
-      <c r="B46">
+      <c r="B111" s="6">
         <f ca="1"/>
         <v>112</v>
       </c>
-      <c r="C46" s="6" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A47" s="3" vm="3">
+      <c r="C111">
+        <f ca="1"/>
+        <v>111.95999796199298</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A112" s="3" vm="3">
         <f ca="1"/>
         <v>17930</v>
       </c>
-      <c r="B47">
+      <c r="B112" s="6">
         <f ca="1"/>
         <v>118</v>
       </c>
-      <c r="C47" s="6" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A48" s="3" vm="4">
+      <c r="C112">
+        <f ca="1"/>
+        <v>120.19333660189936</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A113" s="3" vm="4">
         <f ca="1"/>
         <v>17958</v>
       </c>
-      <c r="B48">
+      <c r="B113" s="6">
         <f ca="1"/>
         <v>132</v>
       </c>
-      <c r="C48" s="6" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A49" s="3" vm="5">
+      <c r="C113">
+        <f ca="1"/>
+        <v>134.67683544691363</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A114" s="3" vm="5">
         <f ca="1"/>
         <v>17989</v>
       </c>
-      <c r="B49">
+      <c r="B114" s="6">
         <f ca="1"/>
         <v>129</v>
       </c>
-      <c r="C49" s="6" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A50" s="3" vm="6">
+      <c r="C114">
+        <f ca="1"/>
+        <v>131.40726345798356</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A115" s="3" vm="6">
         <f ca="1"/>
         <v>18019</v>
       </c>
-      <c r="B50">
+      <c r="B115" s="6">
         <f ca="1"/>
         <v>121</v>
       </c>
-      <c r="C50" s="6" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A51" s="3" vm="13">
+      <c r="C115">
+        <f ca="1"/>
+        <v>124.64374307768698</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A116" s="3" vm="13">
         <f ca="1"/>
         <v>18050</v>
       </c>
-      <c r="B51">
+      <c r="B116" s="6">
         <f ca="1"/>
         <v>135</v>
       </c>
-      <c r="C51" s="6" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A52" s="3" vm="14">
+      <c r="C116">
+        <f ca="1"/>
+        <v>140.4272455247596</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A117" s="3" vm="14">
         <f ca="1"/>
         <v>18080</v>
       </c>
-      <c r="B52">
+      <c r="B117" s="6">
         <f ca="1"/>
         <v>148</v>
       </c>
-      <c r="C52" s="6" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A53" s="3" vm="15">
+      <c r="C117">
+        <f ca="1"/>
+        <v>153.85808678698692</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A118" s="3" vm="15">
         <f ca="1"/>
         <v>18111</v>
       </c>
-      <c r="B53">
+      <c r="B118" s="6">
         <f ca="1"/>
         <v>148</v>
       </c>
-      <c r="C53" s="6" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A54" s="3" vm="16">
+      <c r="C118">
+        <f ca="1"/>
+        <v>152.4364177143994</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A119" s="3" vm="16">
         <f ca="1"/>
         <v>18142</v>
       </c>
-      <c r="B54">
+      <c r="B119" s="6">
         <f ca="1"/>
         <v>136</v>
       </c>
-      <c r="C54" s="6" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A55" s="3" vm="17">
+      <c r="C119">
+        <f ca="1"/>
+        <v>139.68358943158842</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A120" s="3" vm="17">
         <f ca="1"/>
         <v>18172</v>
       </c>
-      <c r="B55">
+      <c r="B120">
         <f ca="1"/>
         <v>119</v>
       </c>
-      <c r="C55" s="6" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A56" s="3" vm="18">
-        <f ca="1"/>
-        <v>18203</v>
-      </c>
-      <c r="B56">
-        <f ca="1"/>
-        <v>104</v>
-      </c>
-      <c r="C56" s="6" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A57" s="3" vm="19">
-        <f ca="1"/>
-        <v>18233</v>
-      </c>
-      <c r="B57">
-        <f ca="1"/>
-        <v>118</v>
-      </c>
-      <c r="C57" s="6">
-        <f ca="1"/>
-        <v>126.66666666666667</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="C58" s="6"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A60" s="3" t="e" cm="1" vm="20">
-        <f t="array" aca="1" ref="A60" ca="1">_xlfn._xlws.PY(4,0)</f>
+      <c r="C120">
+        <f ca="1"/>
+        <v>122.38855242329556</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A121" s="3" t="e" cm="1" vm="25">
+        <f t="array" aca="1" ref="A121" ca="1">_xlfn._xlws.PY(8,1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A86" s="3" t="str" cm="1">
-        <f t="array" aca="1" ref="A86:B101" ca="1">_xlfn._xlws.PY(5,0)</f>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A125" s="3" t="e" cm="1" vm="26">
+        <f t="array" aca="1" ref="A125" ca="1">_xlfn._xlws.PY(9,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A127" s="3" t="e" cm="1" vm="27">
+        <f t="array" aca="1" ref="A127" ca="1">_xlfn._xlws.PY(10,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.7">
+      <c r="A134" s="3" t="e" cm="1" vm="26">
+        <f t="array" aca="1" ref="A134" ca="1">_xlfn._xlws.PY(11,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.7">
+      <c r="A142" s="3" t="e" cm="1" vm="28">
+        <f t="array" aca="1" ref="A142" ca="1">_xlfn._xlws.PY(12,1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.7">
+      <c r="A144" s="3" t="e" cm="1" vm="29">
+        <f t="array" aca="1" ref="A144" ca="1">_xlfn._xlws.PY(13,1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A146" s="3" t="str" cm="1">
+        <f t="array" aca="1" ref="A146:C152" ca="1">_xlfn._xlws.PY(14,0)</f>
+        <v/>
+      </c>
+      <c r="B146" s="6" t="str">
+        <f ca="1"/>
+        <v>passengers</v>
+      </c>
+      <c r="C146" t="str">
+        <f ca="1"/>
+        <v>forecast</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A147" s="3" t="str">
+        <f ca="1"/>
         <v>date</v>
       </c>
-      <c r="B86" s="5" t="str">
-        <f ca="1"/>
-        <v>trend</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A87" s="3" vm="2">
-        <f ca="1"/>
-        <v>17899</v>
-      </c>
-      <c r="B87" s="5" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A88" s="3" vm="3">
-        <f ca="1"/>
-        <v>17930</v>
-      </c>
-      <c r="B88" s="5" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A89" s="3" vm="4">
-        <f ca="1"/>
-        <v>17958</v>
-      </c>
-      <c r="B89" s="5" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A90" s="3" vm="5">
-        <f ca="1"/>
-        <v>17989</v>
-      </c>
-      <c r="B90" s="5" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A91" s="3" vm="6">
-        <f ca="1"/>
-        <v>18019</v>
-      </c>
-      <c r="B91" s="5" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A92" s="3" vm="13">
-        <f ca="1"/>
-        <v>18050</v>
-      </c>
-      <c r="B92" s="5" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A93" s="3" vm="14">
-        <f ca="1"/>
-        <v>18080</v>
-      </c>
-      <c r="B93" s="5">
-        <f ca="1"/>
-        <v>126.79166666666666</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A94" s="3" vm="15">
-        <f ca="1"/>
-        <v>18111</v>
-      </c>
-      <c r="B94" s="5">
-        <f ca="1"/>
-        <v>127.24999999999999</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A95" s="3" vm="16">
-        <f ca="1"/>
-        <v>18142</v>
-      </c>
-      <c r="B95" s="5">
-        <f ca="1"/>
-        <v>127.95833333333331</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A96" s="3" vm="17">
-        <f ca="1"/>
-        <v>18172</v>
-      </c>
-      <c r="B96" s="5">
-        <f ca="1"/>
-        <v>128.58333333333331</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A97" s="3" vm="18">
-        <f ca="1"/>
-        <v>18203</v>
-      </c>
-      <c r="B97" s="5">
-        <f ca="1"/>
-        <v>128.99999999999997</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A98" s="3" vm="19">
-        <f ca="1"/>
-        <v>18233</v>
-      </c>
-      <c r="B98" s="5">
-        <f ca="1"/>
-        <v>129.75</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A99" s="3" vm="21">
-        <f ca="1"/>
-        <v>18264</v>
-      </c>
-      <c r="B99" s="5">
-        <f ca="1"/>
-        <v>131.25</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A100" s="3" vm="22">
-        <f ca="1"/>
-        <v>18295</v>
-      </c>
-      <c r="B100" s="5">
-        <f ca="1"/>
-        <v>133.08333333333334</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A101" s="3" vm="23">
-        <f ca="1"/>
-        <v>18323</v>
-      </c>
-      <c r="B101" s="5">
-        <f ca="1"/>
-        <v>134.91666666666669</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A104" s="3" t="e" cm="1" vm="24">
-        <f t="array" aca="1" ref="A104" ca="1">_xlfn._xlws.PY(6,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="B119" s="6"/>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A120" s="3" t="str" cm="1">
-        <f t="array" aca="1" ref="A120:C131" ca="1">_xlfn._xlws.PY(7,0)</f>
+      <c r="B147" s="6" t="str">
+        <f ca="1"/>
         <v/>
       </c>
-      <c r="B120" s="6" t="str">
-        <f ca="1"/>
-        <v>passengers</v>
-      </c>
-      <c r="C120" t="str">
-        <f ca="1"/>
-        <v>fitted</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A121" s="3" t="str">
-        <f ca="1"/>
-        <v>date</v>
-      </c>
-      <c r="B121" s="6" t="str">
+      <c r="C147" t="str">
         <f ca="1"/>
         <v/>
       </c>
-      <c r="C121" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A122" s="3" vm="2">
-        <f ca="1"/>
-        <v>17899</v>
-      </c>
-      <c r="B122" s="6">
-        <f ca="1"/>
-        <v>112</v>
-      </c>
-      <c r="C122">
-        <f ca="1"/>
-        <v>111.95999796199298</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A123" s="3" vm="3">
-        <f ca="1"/>
-        <v>17930</v>
-      </c>
-      <c r="B123" s="6">
-        <f ca="1"/>
-        <v>118</v>
-      </c>
-      <c r="C123">
-        <f ca="1"/>
-        <v>120.19333660189936</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A124" s="3" vm="4">
-        <f ca="1"/>
-        <v>17958</v>
-      </c>
-      <c r="B124" s="6">
-        <f ca="1"/>
-        <v>132</v>
-      </c>
-      <c r="C124">
-        <f ca="1"/>
-        <v>134.67683544691363</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A125" s="3" vm="5">
-        <f ca="1"/>
-        <v>17989</v>
-      </c>
-      <c r="B125" s="6">
-        <f ca="1"/>
-        <v>129</v>
-      </c>
-      <c r="C125">
-        <f ca="1"/>
-        <v>131.40726345798356</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A126" s="3" vm="6">
-        <f ca="1"/>
-        <v>18019</v>
-      </c>
-      <c r="B126" s="6">
-        <f ca="1"/>
-        <v>121</v>
-      </c>
-      <c r="C126">
-        <f ca="1"/>
-        <v>124.64374307768698</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A127" s="3" vm="13">
-        <f ca="1"/>
-        <v>18050</v>
-      </c>
-      <c r="B127" s="6">
-        <f ca="1"/>
-        <v>135</v>
-      </c>
-      <c r="C127">
-        <f ca="1"/>
-        <v>140.4272455247596</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A128" s="3" vm="14">
-        <f ca="1"/>
-        <v>18080</v>
-      </c>
-      <c r="B128" s="6">
-        <f ca="1"/>
-        <v>148</v>
-      </c>
-      <c r="C128">
-        <f ca="1"/>
-        <v>153.85808678698692</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A129" s="3" vm="15">
-        <f ca="1"/>
-        <v>18111</v>
-      </c>
-      <c r="B129" s="6">
-        <f ca="1"/>
-        <v>148</v>
-      </c>
-      <c r="C129">
-        <f ca="1"/>
-        <v>152.4364177143994</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A130" s="3" vm="16">
-        <f ca="1"/>
-        <v>18142</v>
-      </c>
-      <c r="B130" s="6">
-        <f ca="1"/>
-        <v>136</v>
-      </c>
-      <c r="C130">
-        <f ca="1"/>
-        <v>139.68358943158842</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A131" s="3" vm="17">
-        <f ca="1"/>
-        <v>18172</v>
-      </c>
-      <c r="B131">
-        <f ca="1"/>
-        <v>119</v>
-      </c>
-      <c r="C131">
-        <f ca="1"/>
-        <v>122.38855242329556</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A132" s="3" t="e" cm="1" vm="25">
-        <f t="array" aca="1" ref="A132" ca="1">_xlfn._xlws.PY(8,1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A136" s="3" t="e" cm="1" vm="26">
-        <f t="array" aca="1" ref="A136" ca="1">_xlfn._xlws.PY(9,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A138" s="3" t="e" cm="1" vm="27">
-        <f t="array" aca="1" ref="A138" ca="1">_xlfn._xlws.PY(10,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A145" s="3" t="e" cm="1" vm="26">
-        <f t="array" aca="1" ref="A145" ca="1">_xlfn._xlws.PY(11,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A153" s="3" t="str" cm="1">
-        <f t="array" aca="1" ref="A153:B155" ca="1">_xlfn._xlws.PY(12,0)</f>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A148" s="3" vm="30">
+        <f ca="1"/>
+        <v>21551</v>
+      </c>
+      <c r="B148" s="6">
+        <f ca="1"/>
+        <v>360</v>
+      </c>
+      <c r="C148">
+        <f ca="1"/>
+        <v>354.17364147573602</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A149" s="3" vm="31">
+        <f ca="1"/>
+        <v>21582</v>
+      </c>
+      <c r="B149" s="6">
+        <f ca="1"/>
+        <v>342</v>
+      </c>
+      <c r="C149">
+        <f ca="1"/>
+        <v>337.57319653024558</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A150" s="3" vm="32">
+        <f ca="1"/>
+        <v>21610</v>
+      </c>
+      <c r="B150" s="6">
+        <f ca="1"/>
+        <v>406</v>
+      </c>
+      <c r="C150">
+        <f ca="1"/>
+        <v>387.7744448625624</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A151" s="3" vm="33">
+        <f ca="1"/>
+        <v>21641</v>
+      </c>
+      <c r="B151">
+        <f ca="1"/>
+        <v>396</v>
+      </c>
+      <c r="C151">
+        <f ca="1"/>
+        <v>379.77500904445122</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A152" s="3" vm="34">
+        <f ca="1"/>
+        <v>21671</v>
+      </c>
+      <c r="B152">
+        <f ca="1"/>
+        <v>420</v>
+      </c>
+      <c r="C152">
+        <f ca="1"/>
+        <v>397.21314537513348</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A154" s="3" t="str" cm="1" vm="35">
+        <f t="array" aca="1" ref="A154" ca="1">_xlfn._xlws.PY(15,1)</f>
+        <v>Mean Absolute Error: 31.07</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A157" s="3" t="str" cm="1">
+        <f t="array" aca="1" ref="A157:C169" ca="1">_xlfn._xlws.PY(16,0)</f>
+        <v>Actual</v>
+      </c>
+      <c r="B157" s="6" t="str">
+        <f ca="1"/>
+        <v>Forecast</v>
+      </c>
+      <c r="C157" s="6" t="str">
+        <f ca="1"/>
+        <v>Error</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A158" s="3">
+        <f ca="1"/>
+        <v>360</v>
+      </c>
+      <c r="B158" s="6">
+        <f ca="1"/>
+        <v>354.17364147573602</v>
+      </c>
+      <c r="C158" s="6">
+        <f ca="1"/>
+        <v>5.8263585242639806</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A159" s="3">
+        <f ca="1"/>
+        <v>342</v>
+      </c>
+      <c r="B159" s="6">
+        <f ca="1"/>
+        <v>337.57319653024558</v>
+      </c>
+      <c r="C159" s="6">
+        <f ca="1"/>
+        <v>4.4268034697544181</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A160" s="3">
+        <f ca="1"/>
+        <v>406</v>
+      </c>
+      <c r="B160" s="6">
+        <f ca="1"/>
+        <v>387.7744448625624</v>
+      </c>
+      <c r="C160" s="6">
+        <f ca="1"/>
+        <v>18.225555137437595</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A161" s="3">
+        <f ca="1"/>
+        <v>396</v>
+      </c>
+      <c r="B161" s="6">
+        <f ca="1"/>
+        <v>379.77500904445122</v>
+      </c>
+      <c r="C161" s="6">
+        <f ca="1"/>
+        <v>16.224990955548776</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A162" s="3">
+        <f ca="1"/>
+        <v>420</v>
+      </c>
+      <c r="B162" s="6">
+        <f ca="1"/>
+        <v>397.21314537513348</v>
+      </c>
+      <c r="C162" s="6">
+        <f ca="1"/>
+        <v>22.786854624866521</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A163" s="3">
+        <f ca="1"/>
+        <v>472</v>
+      </c>
+      <c r="B163" s="6">
+        <f ca="1"/>
+        <v>468.87706028701018</v>
+      </c>
+      <c r="C163" s="6">
+        <f ca="1"/>
+        <v>3.1229397129898189</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A164" s="3">
+        <f ca="1"/>
+        <v>548</v>
+      </c>
+      <c r="B164" s="6">
+        <f ca="1"/>
+        <v>520.42527545650694</v>
+      </c>
+      <c r="C164" s="6">
+        <f ca="1"/>
+        <v>27.574724543493062</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A165" s="3">
+        <f ca="1"/>
+        <v>559</v>
+      </c>
+      <c r="B165" s="6">
+        <f ca="1"/>
+        <v>526.51011146486042</v>
+      </c>
+      <c r="C165" s="6">
+        <f ca="1"/>
+        <v>32.489888535139585</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A166" s="3">
+        <f ca="1"/>
+        <v>463</v>
+      </c>
+      <c r="B166" s="6">
+        <f ca="1"/>
+        <v>427.87427734740862</v>
+      </c>
+      <c r="C166" s="6">
+        <f ca="1"/>
+        <v>35.125722652591378</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A167" s="3">
+        <f ca="1"/>
+        <v>407</v>
+      </c>
+      <c r="B167" s="6">
+        <f ca="1"/>
+        <v>381.94210181918794</v>
+      </c>
+      <c r="C167" s="6">
+        <f ca="1"/>
+        <v>25.05789818081206</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A168" s="3">
+        <f ca="1"/>
+        <v>362</v>
+      </c>
+      <c r="B168" s="6">
+        <f ca="1"/>
+        <v>334.44886906567876</v>
+      </c>
+      <c r="C168" s="6">
+        <f ca="1"/>
+        <v>27.551130934321236</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A169" s="3">
+        <f ca="1"/>
+        <v>405</v>
+      </c>
+      <c r="B169" s="6">
+        <f ca="1"/>
+        <v>373.5830131238987</v>
+      </c>
+      <c r="C169" s="6">
+        <f ca="1"/>
+        <v>31.416986876101305</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A173" s="3" t="str" cm="1" vm="36">
+        <f t="array" aca="1" ref="A173" ca="1">_xlfn._xlws.PY(17,1)</f>
+        <v>Baseline MAE: 115.25</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A176" s="3" t="str" cm="1">
+        <f t="array" aca="1" ref="A176:B179" ca="1">_xlfn._xlws.PY(18,0)</f>
         <v>Metric</v>
       </c>
-      <c r="B153" t="str">
+      <c r="B176" t="str">
         <f ca="1"/>
         <v>Value</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A154" s="3" t="str">
-        <f ca="1"/>
-        <v>Test Statistic</v>
-      </c>
-      <c r="B154" s="6">
-        <f ca="1"/>
-        <v>0.81536887920606549</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A155" s="3" t="str">
-        <f ca="1"/>
-        <v>p-value</v>
-      </c>
-      <c r="B155" s="6">
-        <f ca="1"/>
-        <v>0.99188024343764125</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A157" s="3" t="e" cm="1" vm="28">
-        <f t="array" aca="1" ref="A157" ca="1">_xlfn._xlws.PY(13,1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A159" s="3" t="e" cm="1" vm="29">
-        <f t="array" aca="1" ref="A159" ca="1">_xlfn._xlws.PY(14,1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A161" s="3" cm="1" vm="30">
-        <f t="array" aca="1" ref="A161:B165" ca="1">_xlfn._xlws.PY(15,0)</f>
-        <v>21551</v>
-      </c>
-      <c r="B161" s="6">
-        <f ca="1"/>
-        <v>354.17364147573602</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A162" s="3" vm="31">
-        <f ca="1"/>
-        <v>21582</v>
-      </c>
-      <c r="B162" s="6">
-        <f ca="1"/>
-        <v>337.57319653024558</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A163" s="3" vm="32">
-        <f ca="1"/>
-        <v>21610</v>
-      </c>
-      <c r="B163" s="6">
-        <f ca="1"/>
-        <v>387.7744448625624</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A164" s="3" vm="33">
-        <f ca="1"/>
-        <v>21641</v>
-      </c>
-      <c r="B164" s="6">
-        <f ca="1"/>
-        <v>379.77500904445122</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A165" s="3" vm="34">
-        <f ca="1"/>
-        <v>21671</v>
-      </c>
-      <c r="B165" s="6">
-        <f ca="1"/>
-        <v>397.21314537513348</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A168" s="3" t="str" cm="1" vm="35">
-        <f t="array" aca="1" ref="A168" ca="1">_xlfn._xlws.PY(16,1)</f>
-        <v>Mean Absolute Error: 31.07</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A171" s="3" t="str" cm="1">
-        <f t="array" aca="1" ref="A171:C183" ca="1">_xlfn._xlws.PY(17,0)</f>
-        <v>Actual</v>
-      </c>
-      <c r="B171" s="6" t="str">
-        <f ca="1"/>
-        <v>Forecast</v>
-      </c>
-      <c r="C171" s="6" t="str">
-        <f ca="1"/>
-        <v>Error</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A172" s="3">
-        <f ca="1"/>
-        <v>360</v>
-      </c>
-      <c r="B172" s="6">
-        <f ca="1"/>
-        <v>354.17364147573602</v>
-      </c>
-      <c r="C172" s="6">
-        <f ca="1"/>
-        <v>5.8263585242639806</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A173" s="3">
-        <f ca="1"/>
-        <v>342</v>
-      </c>
-      <c r="B173" s="6">
-        <f ca="1"/>
-        <v>337.57319653024558</v>
-      </c>
-      <c r="C173" s="6">
-        <f ca="1"/>
-        <v>4.4268034697544181</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A174" s="3">
-        <f ca="1"/>
-        <v>406</v>
-      </c>
-      <c r="B174" s="6">
-        <f ca="1"/>
-        <v>387.7744448625624</v>
-      </c>
-      <c r="C174" s="6">
-        <f ca="1"/>
-        <v>18.225555137437595</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A175" s="3">
-        <f ca="1"/>
-        <v>396</v>
-      </c>
-      <c r="B175" s="6">
-        <f ca="1"/>
-        <v>379.77500904445122</v>
-      </c>
-      <c r="C175" s="6">
-        <f ca="1"/>
-        <v>16.224990955548776</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A176" s="3">
-        <f ca="1"/>
-        <v>420</v>
-      </c>
-      <c r="B176" s="6">
-        <f ca="1"/>
-        <v>397.21314537513348</v>
-      </c>
-      <c r="C176" s="6">
-        <f ca="1"/>
-        <v>22.786854624866521</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A177" s="3">
-        <f ca="1"/>
-        <v>472</v>
-      </c>
-      <c r="B177" s="6">
-        <f ca="1"/>
-        <v>468.87706028701018</v>
-      </c>
-      <c r="C177" s="6">
-        <f ca="1"/>
-        <v>3.1229397129898189</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A178" s="3">
-        <f ca="1"/>
-        <v>548</v>
-      </c>
-      <c r="B178" s="6">
-        <f ca="1"/>
-        <v>520.42527545650694</v>
-      </c>
-      <c r="C178" s="6">
-        <f ca="1"/>
-        <v>27.574724543493062</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A179" s="3">
-        <f ca="1"/>
-        <v>559</v>
-      </c>
-      <c r="B179" s="6">
-        <f ca="1"/>
-        <v>526.51011146486042</v>
-      </c>
-      <c r="C179" s="6">
-        <f ca="1"/>
-        <v>32.489888535139585</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A180" s="3">
-        <f ca="1"/>
-        <v>463</v>
-      </c>
-      <c r="B180" s="6">
-        <f ca="1"/>
-        <v>427.87427734740862</v>
-      </c>
-      <c r="C180" s="6">
-        <f ca="1"/>
-        <v>35.125722652591378</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A181" s="3">
-        <f ca="1"/>
-        <v>407</v>
-      </c>
-      <c r="B181" s="6">
-        <f ca="1"/>
-        <v>381.94210181918794</v>
-      </c>
-      <c r="C181" s="6">
-        <f ca="1"/>
-        <v>25.05789818081206</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A182" s="3">
-        <f ca="1"/>
-        <v>362</v>
-      </c>
-      <c r="B182" s="6">
-        <f ca="1"/>
-        <v>334.44886906567876</v>
-      </c>
-      <c r="C182" s="6">
-        <f ca="1"/>
-        <v>27.551130934321236</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A183" s="3">
-        <f ca="1"/>
-        <v>405</v>
-      </c>
-      <c r="B183" s="6">
-        <f ca="1"/>
-        <v>373.5830131238987</v>
-      </c>
-      <c r="C183" s="6">
-        <f ca="1"/>
-        <v>31.416986876101305</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A187" s="3" cm="1" vm="36">
-        <f t="array" aca="1" ref="A187" ca="1">_xlfn._xlws.PY(18,1)</f>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A177" s="3" t="str">
+        <f ca="1"/>
+        <v>Holt-Winters MAE</v>
+      </c>
+      <c r="B177">
+        <f ca="1"/>
+        <v>31.07</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A178" s="3" t="str">
+        <f ca="1"/>
+        <v>Baseline MAE</v>
+      </c>
+      <c r="B178">
+        <f ca="1"/>
         <v>115.25</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A190" s="3" t="str" cm="1">
-        <f t="array" aca="1" ref="A190:B193" ca="1">_xlfn._xlws.PY(19,0)</f>
-        <v>Metric</v>
-      </c>
-      <c r="B190" t="str">
-        <f ca="1"/>
-        <v>Value</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A191" s="3" t="str">
-        <f ca="1"/>
-        <v>Holt-Winters MAE</v>
-      </c>
-      <c r="B191">
-        <f ca="1"/>
-        <v>31.07</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A192" s="3" t="str">
-        <f ca="1"/>
-        <v>Baseline MAE</v>
-      </c>
-      <c r="B192">
-        <f ca="1"/>
-        <v>115.25</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A193" s="3" t="str">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A179" s="3" t="str">
         <f ca="1"/>
         <v>Improvement (%)</v>
       </c>
-      <c r="B193">
+      <c r="B179">
         <f ca="1"/>
         <v>73.040000000000006</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A196" s="3" t="e" cm="1" vm="37">
-        <f t="array" aca="1" ref="A196" ca="1">_xlfn._xlws.PY(20,0)</f>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A182" s="3" t="e" cm="1" vm="37">
+        <f t="array" aca="1" ref="A182" ca="1">_xlfn._xlws.PY(19,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -5491,12 +5488,12 @@
   <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.45703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1:B7" ca="1">_xlfn._xlws.PY(21,0,shampoo[#All])</f>
+        <f t="array" aca="1" ref="A1:B7" ca="1">_xlfn._xlws.PY(20,0,shampoo[#All])</f>
         <v/>
       </c>
       <c r="B1" t="str">
@@ -5566,13 +5563,13 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A10" t="e" cm="1" vm="43">
-        <f t="array" aca="1" ref="A10" ca="1">_xlfn._xlws.PY(22,0)</f>
+        <f t="array" aca="1" ref="A10" ca="1">_xlfn._xlws.PY(21,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.7">
       <c r="A27" t="e" cm="1" vm="44">
-        <f t="array" aca="1" ref="A27" ca="1">_xlfn._xlws.PY(23,0)</f>
+        <f t="array" aca="1" ref="A27" ca="1">_xlfn._xlws.PY(22,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>

--- a/ch_07/ch_07_solutions.xlsx
+++ b/ch_07/ch_07_solutions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30501"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30515"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1118BB5-F6B0-45B5-8C4E-F4F80CC7692B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33449773-73F2-4B7A-8643-823CC0253D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" firstSheet="1" activeTab="1" xr2:uid="{127BCBE3-2501-4C38-9896-5064F2DA9264}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" xr2:uid="{127BCBE3-2501-4C38-9896-5064F2DA9264}"/>
   </bookViews>
   <sheets>
     <sheet name="AirPassengers" sheetId="1" r:id="rId1"/>
@@ -2360,7 +2360,7 @@
   <rv s="3">
     <v>&lt;class 'statsmodels.tsa.holtwinters.results.HoltWintersResultsWrapper'&gt;</v>
     <v>HoltWintersResultsWrapper</v>
-    <v>&lt;statsmodels.tsa.holtwinters.results.HoltWintersResultsWrapper object at 0x7f052781d9a0&gt;</v>
+    <v>&lt;statsmodels.tsa.holtwinters.results.HoltWintersResultsWrapper object at 0x7ff3a312bcb0&gt;</v>
     <v>1</v>
   </rv>
   <rv s="8">
